--- a/20240304_binary_files/output/20240304_binary_files_element_pairs.xlsx
+++ b/20240304_binary_files/output/20240304_binary_files_element_pairs.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rh-Sb" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sb-Sb" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Th-Os" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Os-Os" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Th-Th" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Nd-Si" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Si-Si" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Sb" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Th-Os" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Os-Os" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Th-Th" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Si" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/20240304_binary_files/output/20240304_binary_files_element_pairs.xlsx
+++ b/20240304_binary_files/output/20240304_binary_files_element_pairs.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Sb" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Th-Os" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Os-Os" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Th-Th" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Si" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Rh-Sb" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sb-Sb" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Os-Os" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Th-Os" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Th-Th" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Nd-Si" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Si-Si" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.652</v>
+        <v>2.516</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.198</v>
+        <v>2.728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.728</v>
+        <v>3.198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.082</v>
+        <v>3.08</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/20240304_binary_files/output/20240304_binary_files_element_pairs.xlsx
+++ b/20240304_binary_files/output/20240304_binary_files_element_pairs.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rh-Sb" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Th-Os" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Os-Os" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Nd-Si" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Si-Si" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Sb" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Os-Os" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Th-Os" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Si" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,9 +460,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -475,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,13 +527,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.198</v>
+        <v>2.728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -521,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,13 +598,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.728</v>
+        <v>3.198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.198</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -567,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,13 +669,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.08</v>
+        <v>2.755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -613,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,13 +740,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.755</v>
+        <v>3.08</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
